--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -610,10 +610,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -624,10 +624,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -680,10 +680,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13">
@@ -697,7 +697,7 @@
         <v>0.04</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17">
@@ -753,7 +753,7 @@
         <v>-0.2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18">
@@ -778,10 +778,10 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
@@ -792,10 +792,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -806,10 +806,10 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -823,7 +823,7 @@
         <v>0.23</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -834,10 +834,10 @@
         <v>25</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">
@@ -848,10 +848,10 @@
         <v>25</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
